--- a/data/umr/Resumen UMR Julio 2026_mas_SFE.xlsx
+++ b/data/umr/Resumen UMR Julio 2026_mas_SFE.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9857AE47-B8C8-435A-8FD3-08DB99E3AF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{9857AE47-B8C8-435A-8FD3-08DB99E3AF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DADFD88F-ABFB-4390-AA1D-02528928C0B4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Odometro-Kilometraje" sheetId="1" r:id="rId1"/>
@@ -391,7 +391,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="187">
   <si>
     <t>Control Contador Kilometraje de Trenes</t>
   </si>
@@ -949,6 +949,9 @@
   </si>
   <si>
     <t>Cambio  026 planilla ver 10 actulizada</t>
+  </si>
+  <si>
+    <t>LI-AM</t>
   </si>
 </sst>
 </file>
@@ -2844,7 +2847,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="383">
+  <cellXfs count="384">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
@@ -3750,11 +3753,38 @@
     <xf numFmtId="0" fontId="0" fillId="60" borderId="85" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3801,30 +3831,6 @@
     <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -3837,6 +3843,9 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3864,9 +3873,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -4878,37 +4884,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="344" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="344"/>
-      <c r="C1" s="344"/>
-      <c r="D1" s="344"/>
-      <c r="E1" s="344"/>
-      <c r="F1" s="344"/>
-      <c r="G1" s="344"/>
-      <c r="H1" s="344"/>
-      <c r="I1" s="344"/>
-      <c r="J1" s="344"/>
-      <c r="K1" s="344"/>
-      <c r="L1" s="344"/>
-      <c r="M1" s="344"/>
-      <c r="N1" s="344"/>
-      <c r="O1" s="344"/>
-      <c r="P1" s="344"/>
-      <c r="Q1" s="344"/>
-      <c r="R1" s="344"/>
-      <c r="S1" s="344"/>
-      <c r="T1" s="344"/>
-      <c r="U1" s="344"/>
-      <c r="V1" s="344"/>
-      <c r="W1" s="344"/>
-      <c r="X1" s="344"/>
-      <c r="Y1" s="344"/>
-      <c r="Z1" s="344"/>
-      <c r="AA1" s="344"/>
-      <c r="AB1" s="344"/>
-      <c r="AC1" s="344"/>
+      <c r="A1" s="345" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="345"/>
+      <c r="C1" s="345"/>
+      <c r="D1" s="345"/>
+      <c r="E1" s="345"/>
+      <c r="F1" s="345"/>
+      <c r="G1" s="345"/>
+      <c r="H1" s="345"/>
+      <c r="I1" s="345"/>
+      <c r="J1" s="345"/>
+      <c r="K1" s="345"/>
+      <c r="L1" s="345"/>
+      <c r="M1" s="345"/>
+      <c r="N1" s="345"/>
+      <c r="O1" s="345"/>
+      <c r="P1" s="345"/>
+      <c r="Q1" s="345"/>
+      <c r="R1" s="345"/>
+      <c r="S1" s="345"/>
+      <c r="T1" s="345"/>
+      <c r="U1" s="345"/>
+      <c r="V1" s="345"/>
+      <c r="W1" s="345"/>
+      <c r="X1" s="345"/>
+      <c r="Y1" s="345"/>
+      <c r="Z1" s="345"/>
+      <c r="AA1" s="345"/>
+      <c r="AB1" s="345"/>
+      <c r="AC1" s="345"/>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -7619,37 +7625,37 @@
       <c r="AC46" s="211"/>
     </row>
     <row r="47" spans="1:31" ht="18" x14ac:dyDescent="0.25">
-      <c r="A47" s="344" t="s">
+      <c r="A47" s="345" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="344"/>
-      <c r="C47" s="344"/>
-      <c r="D47" s="344"/>
-      <c r="E47" s="344"/>
-      <c r="F47" s="344"/>
-      <c r="G47" s="344"/>
-      <c r="H47" s="344"/>
-      <c r="I47" s="344"/>
-      <c r="J47" s="344"/>
-      <c r="K47" s="344"/>
-      <c r="L47" s="344"/>
-      <c r="M47" s="344"/>
-      <c r="N47" s="344"/>
-      <c r="O47" s="344"/>
-      <c r="P47" s="344"/>
-      <c r="Q47" s="344"/>
-      <c r="R47" s="344"/>
-      <c r="S47" s="344"/>
-      <c r="T47" s="344"/>
-      <c r="U47" s="344"/>
-      <c r="V47" s="344"/>
-      <c r="W47" s="344"/>
-      <c r="X47" s="344"/>
-      <c r="Y47" s="344"/>
-      <c r="Z47" s="344"/>
-      <c r="AA47" s="344"/>
-      <c r="AB47" s="344"/>
-      <c r="AC47" s="344"/>
+      <c r="B47" s="345"/>
+      <c r="C47" s="345"/>
+      <c r="D47" s="345"/>
+      <c r="E47" s="345"/>
+      <c r="F47" s="345"/>
+      <c r="G47" s="345"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="345"/>
+      <c r="J47" s="345"/>
+      <c r="K47" s="345"/>
+      <c r="L47" s="345"/>
+      <c r="M47" s="345"/>
+      <c r="N47" s="345"/>
+      <c r="O47" s="345"/>
+      <c r="P47" s="345"/>
+      <c r="Q47" s="345"/>
+      <c r="R47" s="345"/>
+      <c r="S47" s="345"/>
+      <c r="T47" s="345"/>
+      <c r="U47" s="345"/>
+      <c r="V47" s="345"/>
+      <c r="W47" s="345"/>
+      <c r="X47" s="345"/>
+      <c r="Y47" s="345"/>
+      <c r="Z47" s="345"/>
+      <c r="AA47" s="345"/>
+      <c r="AB47" s="345"/>
+      <c r="AC47" s="345"/>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48" s="9"/>
@@ -13203,14 +13209,14 @@
     </row>
     <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="367" t="s">
+      <c r="B2" s="347" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="367"/>
-      <c r="D2" s="368" t="s">
+      <c r="C2" s="347"/>
+      <c r="D2" s="348" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="368"/>
+      <c r="E2" s="348"/>
       <c r="F2" s="231" t="s">
         <v>163</v>
       </c>
@@ -13291,64 +13297,73 @@
       <c r="AF2" s="335">
         <v>19</v>
       </c>
+      <c r="AG2" s="231" t="s">
+        <v>186</v>
+      </c>
+      <c r="AH2" s="344">
+        <f>O1-AB2</f>
+        <v>16.73</v>
+      </c>
     </row>
     <row r="3" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="367" t="s">
+      <c r="B3" s="347" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="367"/>
-      <c r="D3" s="368" t="s">
+      <c r="C3" s="347"/>
+      <c r="D3" s="348" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="368"/>
-      <c r="F3" s="345" t="s">
+      <c r="E3" s="348"/>
+      <c r="F3" s="349" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="345" t="s">
+      <c r="G3" s="349" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="345" t="s">
+      <c r="H3" s="349" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="345" t="s">
+      <c r="I3" s="349" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="345" t="s">
+      <c r="J3" s="349" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="345" t="s">
+      <c r="K3" s="349" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="345" t="s">
+      <c r="L3" s="349" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="345" t="s">
+      <c r="M3" s="349" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="352" t="s">
+      <c r="N3" s="361" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="352" t="s">
+      <c r="O3" s="361" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="351"/>
-      <c r="Q3" s="353" t="s">
+      <c r="P3" s="360"/>
+      <c r="Q3" s="362" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="354"/>
-      <c r="S3" s="355"/>
-      <c r="T3" s="356" t="s">
+      <c r="R3" s="363"/>
+      <c r="S3" s="364"/>
+      <c r="T3" s="365" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="357"/>
-      <c r="V3" s="358"/>
-      <c r="W3" s="349" t="s">
+      <c r="U3" s="366"/>
+      <c r="V3" s="367"/>
+      <c r="W3" s="358" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="349" t="s">
+      <c r="X3" s="358" t="s">
         <v>162</v>
       </c>
+      <c r="AG3" s="124"/>
+      <c r="AH3" s="124"/>
     </row>
     <row r="4" spans="1:34" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
@@ -13364,17 +13379,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="345"/>
-      <c r="G4" s="346"/>
-      <c r="H4" s="346"/>
-      <c r="I4" s="345"/>
-      <c r="J4" s="345"/>
-      <c r="K4" s="345"/>
-      <c r="L4" s="345"/>
-      <c r="M4" s="345"/>
-      <c r="N4" s="352"/>
-      <c r="O4" s="352"/>
-      <c r="P4" s="351"/>
+      <c r="F4" s="349"/>
+      <c r="G4" s="355"/>
+      <c r="H4" s="355"/>
+      <c r="I4" s="349"/>
+      <c r="J4" s="349"/>
+      <c r="K4" s="349"/>
+      <c r="L4" s="349"/>
+      <c r="M4" s="349"/>
+      <c r="N4" s="361"/>
+      <c r="O4" s="361"/>
+      <c r="P4" s="360"/>
       <c r="Q4" s="194" t="s">
         <v>140</v>
       </c>
@@ -13393,8 +13408,8 @@
       <c r="V4" s="235" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="350"/>
-      <c r="X4" s="350"/>
+      <c r="W4" s="359"/>
+      <c r="X4" s="359"/>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -15862,8 +15877,8 @@
       <c r="U41" s="216"/>
       <c r="V41" s="228"/>
       <c r="W41" s="185">
-        <f>J41-(T41*($M$2-$K$1)+(U41*($M$2-$M$1)))</f>
-        <v>5036.1500000000005</v>
+        <f>J41-(T41*($M$2-$K$1)+(U41*($M$2-$M$1)))-AH2</f>
+        <v>5019.420000000001</v>
       </c>
       <c r="X41" s="182">
         <f>H41*$M$2</f>
@@ -16213,7 +16228,7 @@
       </c>
       <c r="O46" s="21">
         <f>(W46/N46)*100</f>
-        <v>95.573200408195305</v>
+        <v>95.441871418478684</v>
       </c>
       <c r="P46" s="192"/>
       <c r="Q46" s="181"/>
@@ -16224,7 +16239,7 @@
       <c r="V46" s="181"/>
       <c r="W46" s="193">
         <f>SUM(W40:W45)</f>
-        <v>12175.07</v>
+        <v>12158.34</v>
       </c>
       <c r="X46" s="193">
         <f>SUM(X40:X45)</f>
@@ -17259,7 +17274,7 @@
       </c>
     </row>
     <row r="62" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="366" t="s">
+      <c r="A62" s="346" t="s">
         <v>185</v>
       </c>
       <c r="B62" s="294">
@@ -17331,7 +17346,7 @@
       <c r="AB62" s="124"/>
     </row>
     <row r="63" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A63" s="366"/>
+      <c r="A63" s="346"/>
       <c r="B63" s="294">
         <v>36</v>
       </c>
@@ -17397,7 +17412,7 @@
       <c r="Y63" s="236"/>
     </row>
     <row r="64" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A64" s="366"/>
+      <c r="A64" s="346"/>
       <c r="B64" s="294">
         <v>32</v>
       </c>
@@ -17464,7 +17479,7 @@
       </c>
     </row>
     <row r="65" spans="1:27" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="366"/>
+      <c r="A65" s="346"/>
       <c r="B65" s="294">
         <v>0</v>
       </c>
@@ -17529,7 +17544,7 @@
       </c>
     </row>
     <row r="66" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="366"/>
+      <c r="A66" s="346"/>
       <c r="B66" s="294">
         <v>4</v>
       </c>
@@ -27973,38 +27988,38 @@
     <row r="222" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="223" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223"/>
-      <c r="B223" s="361" t="s">
+      <c r="B223" s="352" t="s">
         <v>56</v>
       </c>
-      <c r="C223" s="362"/>
-      <c r="D223" s="362"/>
-      <c r="E223" s="362"/>
-      <c r="F223" s="362"/>
-      <c r="G223" s="363"/>
+      <c r="C223" s="353"/>
+      <c r="D223" s="353"/>
+      <c r="E223" s="353"/>
+      <c r="F223" s="353"/>
+      <c r="G223" s="354"/>
       <c r="H223" s="289"/>
-      <c r="I223" s="361" t="s">
+      <c r="I223" s="352" t="s">
         <v>57</v>
       </c>
-      <c r="J223" s="362"/>
-      <c r="K223" s="362"/>
-      <c r="L223" s="362"/>
-      <c r="M223" s="362"/>
-      <c r="N223" s="363"/>
-      <c r="P223" s="359" t="s">
+      <c r="J223" s="353"/>
+      <c r="K223" s="353"/>
+      <c r="L223" s="353"/>
+      <c r="M223" s="353"/>
+      <c r="N223" s="354"/>
+      <c r="P223" s="368" t="s">
         <v>139</v>
       </c>
-      <c r="Q223" s="359"/>
-      <c r="R223" s="359"/>
-      <c r="S223" s="360"/>
-      <c r="T223" s="356" t="s">
+      <c r="Q223" s="368"/>
+      <c r="R223" s="368"/>
+      <c r="S223" s="369"/>
+      <c r="T223" s="365" t="s">
         <v>142</v>
       </c>
-      <c r="U223" s="357"/>
-      <c r="V223" s="358"/>
-      <c r="W223" s="347" t="s">
+      <c r="U223" s="366"/>
+      <c r="V223" s="367"/>
+      <c r="W223" s="356" t="s">
         <v>143</v>
       </c>
-      <c r="X223" s="347" t="s">
+      <c r="X223" s="356" t="s">
         <v>162</v>
       </c>
     </row>
@@ -28070,8 +28085,8 @@
       <c r="V224" s="226" t="s">
         <v>146</v>
       </c>
-      <c r="W224" s="348"/>
-      <c r="X224" s="348"/>
+      <c r="W224" s="357"/>
+      <c r="X224" s="357"/>
     </row>
     <row r="225" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
@@ -28157,7 +28172,7 @@
       </c>
       <c r="W225" s="230">
         <f>W11+W18+W25+W32+W39+W46+W53+W60+W67+W74+W81+W88+W95+W102+W109+W116+W123+W130+W137+W144+W151+W158+W165+W172+W179+W186+W193+W200+W207+W214</f>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="X225" s="230">
         <f>X11+X18+X25+X32+X39+X46+X53+X60+X67+X74+X81+X88+X95+X102+X109+X116+X123+X130+X137+X144+X151+X158+X165+X172+X179+X186+X193+X200+X207+X214</f>
@@ -28581,10 +28596,10 @@
     </row>
     <row r="235" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A235" s="24"/>
-      <c r="B235" s="364" t="s">
+      <c r="B235" s="350" t="s">
         <v>55</v>
       </c>
-      <c r="C235" s="365"/>
+      <c r="C235" s="351"/>
       <c r="D235" s="25" t="s">
         <v>65</v>
       </c>
@@ -28760,17 +28775,6 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="27">
-    <mergeCell ref="A62:A66"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="B235:C235"/>
-    <mergeCell ref="B223:G223"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="H3:H4"/>
@@ -28787,6 +28791,17 @@
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="I223:N223"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="B235:C235"/>
+    <mergeCell ref="B223:G223"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A62:A66"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="D187:E192 D180:E185 D173:E178 D194:E199">
     <cfRule type="expression" dxfId="46" priority="190">
@@ -29045,126 +29060,126 @@
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="C1" s="8"/>
-      <c r="D1" s="369">
+      <c r="D1" s="370">
         <v>46204</v>
       </c>
-      <c r="E1" s="369"/>
-      <c r="F1" s="369">
+      <c r="E1" s="370"/>
+      <c r="F1" s="370">
         <v>46205</v>
       </c>
-      <c r="G1" s="369"/>
-      <c r="H1" s="369">
+      <c r="G1" s="370"/>
+      <c r="H1" s="370">
         <v>46206</v>
       </c>
-      <c r="I1" s="369"/>
-      <c r="J1" s="369">
+      <c r="I1" s="370"/>
+      <c r="J1" s="370">
         <v>46207</v>
       </c>
-      <c r="K1" s="369"/>
-      <c r="L1" s="369">
+      <c r="K1" s="370"/>
+      <c r="L1" s="370">
         <v>46208</v>
       </c>
-      <c r="M1" s="369"/>
-      <c r="N1" s="369">
+      <c r="M1" s="370"/>
+      <c r="N1" s="370">
         <v>46209</v>
       </c>
-      <c r="O1" s="369"/>
-      <c r="P1" s="369">
+      <c r="O1" s="370"/>
+      <c r="P1" s="370">
         <v>46210</v>
       </c>
-      <c r="Q1" s="369"/>
-      <c r="R1" s="369">
+      <c r="Q1" s="370"/>
+      <c r="R1" s="370">
         <v>46211</v>
       </c>
-      <c r="S1" s="369"/>
-      <c r="T1" s="369">
+      <c r="S1" s="370"/>
+      <c r="T1" s="370">
         <v>46212</v>
       </c>
-      <c r="U1" s="369"/>
-      <c r="V1" s="369">
+      <c r="U1" s="370"/>
+      <c r="V1" s="370">
         <v>46213</v>
       </c>
-      <c r="W1" s="369"/>
-      <c r="X1" s="369">
+      <c r="W1" s="370"/>
+      <c r="X1" s="370">
         <v>46214</v>
       </c>
-      <c r="Y1" s="369"/>
-      <c r="Z1" s="369">
+      <c r="Y1" s="370"/>
+      <c r="Z1" s="370">
         <v>46215</v>
       </c>
-      <c r="AA1" s="369"/>
-      <c r="AB1" s="369">
+      <c r="AA1" s="370"/>
+      <c r="AB1" s="370">
         <v>46216</v>
       </c>
-      <c r="AC1" s="369"/>
-      <c r="AD1" s="369">
+      <c r="AC1" s="370"/>
+      <c r="AD1" s="370">
         <v>46217</v>
       </c>
-      <c r="AE1" s="369"/>
-      <c r="AF1" s="369">
+      <c r="AE1" s="370"/>
+      <c r="AF1" s="370">
         <v>46218</v>
       </c>
-      <c r="AG1" s="369"/>
-      <c r="AH1" s="369">
+      <c r="AG1" s="370"/>
+      <c r="AH1" s="370">
         <v>46219</v>
       </c>
-      <c r="AI1" s="369"/>
-      <c r="AJ1" s="369">
+      <c r="AI1" s="370"/>
+      <c r="AJ1" s="370">
         <v>46220</v>
       </c>
-      <c r="AK1" s="369"/>
-      <c r="AL1" s="369">
+      <c r="AK1" s="370"/>
+      <c r="AL1" s="370">
         <v>46221</v>
       </c>
-      <c r="AM1" s="369"/>
-      <c r="AN1" s="369">
+      <c r="AM1" s="370"/>
+      <c r="AN1" s="370">
         <v>46222</v>
       </c>
-      <c r="AO1" s="369"/>
-      <c r="AP1" s="369">
+      <c r="AO1" s="370"/>
+      <c r="AP1" s="370">
         <v>46223</v>
       </c>
-      <c r="AQ1" s="369"/>
-      <c r="AR1" s="369">
+      <c r="AQ1" s="370"/>
+      <c r="AR1" s="370">
         <v>46224</v>
       </c>
-      <c r="AS1" s="369"/>
-      <c r="AT1" s="369">
+      <c r="AS1" s="370"/>
+      <c r="AT1" s="370">
         <v>46225</v>
       </c>
-      <c r="AU1" s="369"/>
-      <c r="AV1" s="369">
+      <c r="AU1" s="370"/>
+      <c r="AV1" s="370">
         <v>46226</v>
       </c>
-      <c r="AW1" s="369"/>
-      <c r="AX1" s="369">
+      <c r="AW1" s="370"/>
+      <c r="AX1" s="370">
         <v>46227</v>
       </c>
-      <c r="AY1" s="369"/>
-      <c r="AZ1" s="369">
+      <c r="AY1" s="370"/>
+      <c r="AZ1" s="370">
         <v>46228</v>
       </c>
-      <c r="BA1" s="369"/>
-      <c r="BB1" s="369">
+      <c r="BA1" s="370"/>
+      <c r="BB1" s="370">
         <v>46229</v>
       </c>
-      <c r="BC1" s="369"/>
-      <c r="BD1" s="369">
+      <c r="BC1" s="370"/>
+      <c r="BD1" s="370">
         <v>46230</v>
       </c>
-      <c r="BE1" s="369"/>
-      <c r="BF1" s="369">
+      <c r="BE1" s="370"/>
+      <c r="BF1" s="370">
         <v>46231</v>
       </c>
-      <c r="BG1" s="369"/>
-      <c r="BH1" s="369">
+      <c r="BG1" s="370"/>
+      <c r="BH1" s="370">
         <v>46232</v>
       </c>
-      <c r="BI1" s="369"/>
-      <c r="BJ1" s="369">
+      <c r="BI1" s="370"/>
+      <c r="BJ1" s="370">
         <v>46233</v>
       </c>
-      <c r="BK1" s="369"/>
+      <c r="BK1" s="370"/>
     </row>
     <row r="2" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="8"/>
@@ -33594,10 +33609,10 @@
       </c>
     </row>
     <row r="37" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A37" s="370" t="s">
+      <c r="A37" s="371" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="370"/>
+      <c r="B37" s="371"/>
       <c r="C37" s="8"/>
       <c r="D37" s="149">
         <f t="shared" ref="D37:AI37" si="14">SUM(D31:D36)</f>
@@ -36054,21 +36069,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="X1:Y1"/>
     <mergeCell ref="BH1:BI1"/>
     <mergeCell ref="BJ1:BK1"/>
     <mergeCell ref="AB1:AC1"/>
@@ -36085,6 +36085,21 @@
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AZ1:BA1"/>
     <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="X1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -39783,19 +39798,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="44.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="371" t="s">
+      <c r="A2" s="372" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="372"/>
-      <c r="C2" s="372"/>
-      <c r="D2" s="372"/>
-      <c r="E2" s="372"/>
-      <c r="F2" s="372"/>
-      <c r="G2" s="372"/>
-      <c r="H2" s="372"/>
-      <c r="I2" s="372"/>
-      <c r="J2" s="372"/>
-      <c r="K2" s="372"/>
+      <c r="B2" s="373"/>
+      <c r="C2" s="373"/>
+      <c r="D2" s="373"/>
+      <c r="E2" s="373"/>
+      <c r="F2" s="373"/>
+      <c r="G2" s="373"/>
+      <c r="H2" s="373"/>
+      <c r="I2" s="373"/>
+      <c r="J2" s="373"/>
+      <c r="K2" s="373"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="158" t="s">
@@ -40056,15 +40071,15 @@
       </c>
       <c r="D9" s="311">
         <f>'KM-Servicio'!W46</f>
-        <v>12175.07</v>
+        <v>12158.34</v>
       </c>
       <c r="E9" s="311">
         <f t="shared" si="1"/>
-        <v>60821.450000000004</v>
+        <v>60804.72</v>
       </c>
       <c r="F9" s="312">
         <f>'KM-Servicio'!O46</f>
-        <v>95.573200408195305</v>
+        <v>95.441871418478684</v>
       </c>
       <c r="G9" s="313">
         <f>SUM('KM-Servicio'!B46:C46)</f>
@@ -40102,7 +40117,7 @@
       </c>
       <c r="E10" s="311">
         <f t="shared" si="1"/>
-        <v>72947.540000000008</v>
+        <v>72930.81</v>
       </c>
       <c r="F10" s="312">
         <f>'KM-Servicio'!O53</f>
@@ -40144,7 +40159,7 @@
       </c>
       <c r="E11" s="311">
         <f t="shared" si="1"/>
-        <v>85105.950000000012</v>
+        <v>85089.22</v>
       </c>
       <c r="F11" s="312">
         <f>'KM-Servicio'!O60</f>
@@ -40186,7 +40201,7 @@
       </c>
       <c r="E12" s="12">
         <f t="shared" si="1"/>
-        <v>96451.24</v>
+        <v>96434.51</v>
       </c>
       <c r="F12" s="166">
         <f>'KM-Servicio'!O67</f>
@@ -40228,7 +40243,7 @@
       </c>
       <c r="E13" s="12">
         <f t="shared" si="1"/>
-        <v>107828.28000000001</v>
+        <v>107811.55</v>
       </c>
       <c r="F13" s="166">
         <f>'KM-Servicio'!O74</f>
@@ -40270,7 +40285,7 @@
       </c>
       <c r="E14" s="12">
         <f t="shared" si="1"/>
-        <v>114297.78000000001</v>
+        <v>114281.05</v>
       </c>
       <c r="F14" s="166">
         <f>'KM-Servicio'!O81</f>
@@ -40312,7 +40327,7 @@
       </c>
       <c r="E15" s="12">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F15" s="166">
         <f>'KM-Servicio'!O88</f>
@@ -40354,7 +40369,7 @@
       </c>
       <c r="E16" s="311">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F16" s="312">
         <f>'KM-Servicio'!O95</f>
@@ -40396,7 +40411,7 @@
       </c>
       <c r="E17" s="311">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F17" s="312" t="e">
         <f>'KM-Servicio'!O102</f>
@@ -40438,7 +40453,7 @@
       </c>
       <c r="E18" s="12">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F18" s="166" t="e">
         <f>'KM-Servicio'!O109</f>
@@ -40480,7 +40495,7 @@
       </c>
       <c r="E19" s="12">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F19" s="166" t="e">
         <f>'KM-Servicio'!O116</f>
@@ -40521,7 +40536,7 @@
       </c>
       <c r="E20" s="12">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F20" s="166" t="e">
         <f>'KM-Servicio'!O123</f>
@@ -40563,7 +40578,7 @@
       </c>
       <c r="E21" s="12">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F21" s="166" t="e">
         <f>'KM-Servicio'!O130</f>
@@ -40605,7 +40620,7 @@
       </c>
       <c r="E22" s="12">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F22" s="171" t="e">
         <f>'KM-Servicio'!O137</f>
@@ -40647,7 +40662,7 @@
       </c>
       <c r="E23" s="311">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F23" s="312" t="e">
         <f>'KM-Servicio'!O144</f>
@@ -40689,7 +40704,7 @@
       </c>
       <c r="E24" s="311">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F24" s="312" t="e">
         <f>'KM-Servicio'!O151</f>
@@ -40731,7 +40746,7 @@
       </c>
       <c r="E25" s="12">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F25" s="166" t="e">
         <f>'KM-Servicio'!O158</f>
@@ -40773,7 +40788,7 @@
       </c>
       <c r="E26" s="12">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F26" s="166" t="e">
         <f>'KM-Servicio'!O165</f>
@@ -40815,7 +40830,7 @@
       </c>
       <c r="E27" s="12">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F27" s="166" t="e">
         <f>'KM-Servicio'!O172</f>
@@ -40857,7 +40872,7 @@
       </c>
       <c r="E28" s="311">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F28" s="312" t="e">
         <f>'KM-Servicio'!O179</f>
@@ -40899,7 +40914,7 @@
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F29" s="166" t="e">
         <f>'KM-Servicio'!O186</f>
@@ -40941,7 +40956,7 @@
       </c>
       <c r="E30" s="311">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F30" s="312" t="e">
         <f>'KM-Servicio'!O193</f>
@@ -40983,7 +40998,7 @@
       </c>
       <c r="E31" s="311">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F31" s="312" t="e">
         <f>'KM-Servicio'!O200</f>
@@ -41025,7 +41040,7 @@
       </c>
       <c r="E32" s="311">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F32" s="312" t="e">
         <f>'KM-Servicio'!O207</f>
@@ -41067,11 +41082,11 @@
       </c>
       <c r="E33" s="311">
         <f t="shared" si="1"/>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O46</f>
-        <v>95.573200408195305</v>
+        <v>95.441871418478684</v>
       </c>
       <c r="G33" s="167">
         <f>'KM-Servicio'!B214+'KM-Servicio'!C214</f>
@@ -41139,11 +41154,11 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>119214.60000000002</v>
+        <v>119197.87000000001</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>2969652.7300000014</v>
+        <v>2969234.4800000018</v>
       </c>
       <c r="F36" s="170" t="e">
         <f>AVERAGE(F4:F34)</f>
@@ -41191,12 +41206,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="373" t="s">
+      <c r="A3" s="375" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="374"/>
-      <c r="C3" s="374"/>
-      <c r="D3" s="375"/>
+      <c r="B3" s="376"/>
+      <c r="C3" s="376"/>
+      <c r="D3" s="377"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="96" t="s">
@@ -41342,12 +41357,12 @@
       <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="376" t="s">
+      <c r="A13" s="378" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="377"/>
-      <c r="C13" s="377"/>
-      <c r="D13" s="378"/>
+      <c r="B13" s="379"/>
+      <c r="C13" s="379"/>
+      <c r="D13" s="380"/>
       <c r="F13" s="140"/>
       <c r="G13" s="141"/>
       <c r="H13" s="141"/>
@@ -41394,8 +41409,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="382"/>
-      <c r="H16" s="382"/>
+      <c r="G16" s="374"/>
+      <c r="H16" s="374"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -41410,8 +41425,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="382"/>
-      <c r="H17" s="382"/>
+      <c r="G17" s="374"/>
+      <c r="H17" s="374"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -41426,8 +41441,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="382"/>
-      <c r="H18" s="382"/>
+      <c r="G18" s="374"/>
+      <c r="H18" s="374"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -41441,8 +41456,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="382"/>
-      <c r="H19" s="382"/>
+      <c r="G19" s="374"/>
+      <c r="H19" s="374"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -41456,8 +41471,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="382"/>
-      <c r="H20" s="382"/>
+      <c r="G20" s="374"/>
+      <c r="H20" s="374"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -41471,8 +41486,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="382"/>
-      <c r="H21" s="382"/>
+      <c r="G21" s="374"/>
+      <c r="H21" s="374"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -41497,9 +41512,9 @@
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="108"/>
-      <c r="B23" s="379"/>
-      <c r="C23" s="380"/>
-      <c r="D23" s="381"/>
+      <c r="B23" s="381"/>
+      <c r="C23" s="382"/>
+      <c r="D23" s="383"/>
       <c r="F23" s="143"/>
       <c r="G23" s="141"/>
       <c r="H23" s="141"/>
@@ -41511,10 +41526,10 @@
       <c r="N23" s="43"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="376"/>
-      <c r="B24" s="377"/>
-      <c r="C24" s="377"/>
-      <c r="D24" s="378"/>
+      <c r="A24" s="378"/>
+      <c r="B24" s="379"/>
+      <c r="C24" s="379"/>
+      <c r="D24" s="380"/>
       <c r="F24" s="141"/>
       <c r="G24" s="141"/>
       <c r="H24" s="141"/>
@@ -41627,9 +41642,9 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="106"/>
-      <c r="B34" s="379"/>
-      <c r="C34" s="380"/>
-      <c r="D34" s="381"/>
+      <c r="B34" s="381"/>
+      <c r="C34" s="382"/>
+      <c r="D34" s="383"/>
       <c r="F34" s="100"/>
       <c r="I34" s="110"/>
     </row>
@@ -41762,17 +41777,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/umr/Resumen UMR Julio 2026_mas_SFE.xlsx
+++ b/data/umr/Resumen UMR Julio 2026_mas_SFE.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{9857AE47-B8C8-435A-8FD3-08DB99E3AF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DADFD88F-ABFB-4390-AA1D-02528928C0B4}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{9857AE47-B8C8-435A-8FD3-08DB99E3AF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14A27736-BB1B-4647-9E24-B83C90217920}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5085" yWindow="3945" windowWidth="21600" windowHeight="11295" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Odometro-Kilometraje" sheetId="1" r:id="rId1"/>
@@ -391,7 +391,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="188">
   <si>
     <t>Control Contador Kilometraje de Trenes</t>
   </si>
@@ -952,6 +952,9 @@
   </si>
   <si>
     <t>LI-AM</t>
+  </si>
+  <si>
+    <t>AM-PU</t>
   </si>
 </sst>
 </file>
@@ -2847,7 +2850,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="384">
+  <cellXfs count="385">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
@@ -3756,35 +3759,14 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3831,6 +3813,30 @@
     <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -3843,9 +3849,6 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3873,6 +3876,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -4884,37 +4890,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="345" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="345"/>
-      <c r="C1" s="345"/>
-      <c r="D1" s="345"/>
-      <c r="E1" s="345"/>
-      <c r="F1" s="345"/>
-      <c r="G1" s="345"/>
-      <c r="H1" s="345"/>
-      <c r="I1" s="345"/>
-      <c r="J1" s="345"/>
-      <c r="K1" s="345"/>
-      <c r="L1" s="345"/>
-      <c r="M1" s="345"/>
-      <c r="N1" s="345"/>
-      <c r="O1" s="345"/>
-      <c r="P1" s="345"/>
-      <c r="Q1" s="345"/>
-      <c r="R1" s="345"/>
-      <c r="S1" s="345"/>
-      <c r="T1" s="345"/>
-      <c r="U1" s="345"/>
-      <c r="V1" s="345"/>
-      <c r="W1" s="345"/>
-      <c r="X1" s="345"/>
-      <c r="Y1" s="345"/>
-      <c r="Z1" s="345"/>
-      <c r="AA1" s="345"/>
-      <c r="AB1" s="345"/>
-      <c r="AC1" s="345"/>
+      <c r="A1" s="346" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="346"/>
+      <c r="C1" s="346"/>
+      <c r="D1" s="346"/>
+      <c r="E1" s="346"/>
+      <c r="F1" s="346"/>
+      <c r="G1" s="346"/>
+      <c r="H1" s="346"/>
+      <c r="I1" s="346"/>
+      <c r="J1" s="346"/>
+      <c r="K1" s="346"/>
+      <c r="L1" s="346"/>
+      <c r="M1" s="346"/>
+      <c r="N1" s="346"/>
+      <c r="O1" s="346"/>
+      <c r="P1" s="346"/>
+      <c r="Q1" s="346"/>
+      <c r="R1" s="346"/>
+      <c r="S1" s="346"/>
+      <c r="T1" s="346"/>
+      <c r="U1" s="346"/>
+      <c r="V1" s="346"/>
+      <c r="W1" s="346"/>
+      <c r="X1" s="346"/>
+      <c r="Y1" s="346"/>
+      <c r="Z1" s="346"/>
+      <c r="AA1" s="346"/>
+      <c r="AB1" s="346"/>
+      <c r="AC1" s="346"/>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -7625,37 +7631,37 @@
       <c r="AC46" s="211"/>
     </row>
     <row r="47" spans="1:31" ht="18" x14ac:dyDescent="0.25">
-      <c r="A47" s="345" t="s">
+      <c r="A47" s="346" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="345"/>
-      <c r="C47" s="345"/>
-      <c r="D47" s="345"/>
-      <c r="E47" s="345"/>
-      <c r="F47" s="345"/>
-      <c r="G47" s="345"/>
-      <c r="H47" s="345"/>
-      <c r="I47" s="345"/>
-      <c r="J47" s="345"/>
-      <c r="K47" s="345"/>
-      <c r="L47" s="345"/>
-      <c r="M47" s="345"/>
-      <c r="N47" s="345"/>
-      <c r="O47" s="345"/>
-      <c r="P47" s="345"/>
-      <c r="Q47" s="345"/>
-      <c r="R47" s="345"/>
-      <c r="S47" s="345"/>
-      <c r="T47" s="345"/>
-      <c r="U47" s="345"/>
-      <c r="V47" s="345"/>
-      <c r="W47" s="345"/>
-      <c r="X47" s="345"/>
-      <c r="Y47" s="345"/>
-      <c r="Z47" s="345"/>
-      <c r="AA47" s="345"/>
-      <c r="AB47" s="345"/>
-      <c r="AC47" s="345"/>
+      <c r="B47" s="346"/>
+      <c r="C47" s="346"/>
+      <c r="D47" s="346"/>
+      <c r="E47" s="346"/>
+      <c r="F47" s="346"/>
+      <c r="G47" s="346"/>
+      <c r="H47" s="346"/>
+      <c r="I47" s="346"/>
+      <c r="J47" s="346"/>
+      <c r="K47" s="346"/>
+      <c r="L47" s="346"/>
+      <c r="M47" s="346"/>
+      <c r="N47" s="346"/>
+      <c r="O47" s="346"/>
+      <c r="P47" s="346"/>
+      <c r="Q47" s="346"/>
+      <c r="R47" s="346"/>
+      <c r="S47" s="346"/>
+      <c r="T47" s="346"/>
+      <c r="U47" s="346"/>
+      <c r="V47" s="346"/>
+      <c r="W47" s="346"/>
+      <c r="X47" s="346"/>
+      <c r="Y47" s="346"/>
+      <c r="Z47" s="346"/>
+      <c r="AA47" s="346"/>
+      <c r="AB47" s="346"/>
+      <c r="AC47" s="346"/>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48" s="9"/>
@@ -13117,7 +13123,7 @@
     <col min="22" max="22" width="7.85546875" style="124" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" s="17"/>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -13207,16 +13213,16 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="347" t="s">
+      <c r="B2" s="369" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="347"/>
-      <c r="D2" s="348" t="s">
+      <c r="C2" s="369"/>
+      <c r="D2" s="370" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="348"/>
+      <c r="E2" s="370"/>
       <c r="F2" s="231" t="s">
         <v>163</v>
       </c>
@@ -13304,68 +13310,75 @@
         <f>O1-AB2</f>
         <v>16.73</v>
       </c>
-    </row>
-    <row r="3" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AI2" s="231" t="s">
+        <v>187</v>
+      </c>
+      <c r="AJ2" s="345">
+        <f>M2-AH2</f>
+        <v>26.400000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="347" t="s">
+      <c r="B3" s="369" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="347"/>
-      <c r="D3" s="348" t="s">
+      <c r="C3" s="369"/>
+      <c r="D3" s="370" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="348"/>
-      <c r="F3" s="349" t="s">
+      <c r="E3" s="370"/>
+      <c r="F3" s="347" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="349" t="s">
+      <c r="G3" s="347" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="349" t="s">
+      <c r="H3" s="347" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="349" t="s">
+      <c r="I3" s="347" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="349" t="s">
+      <c r="J3" s="347" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="349" t="s">
+      <c r="K3" s="347" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="349" t="s">
+      <c r="L3" s="347" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="349" t="s">
+      <c r="M3" s="347" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="361" t="s">
+      <c r="N3" s="354" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="361" t="s">
+      <c r="O3" s="354" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="360"/>
-      <c r="Q3" s="362" t="s">
+      <c r="P3" s="353"/>
+      <c r="Q3" s="355" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="363"/>
-      <c r="S3" s="364"/>
-      <c r="T3" s="365" t="s">
+      <c r="R3" s="356"/>
+      <c r="S3" s="357"/>
+      <c r="T3" s="358" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="366"/>
-      <c r="V3" s="367"/>
-      <c r="W3" s="358" t="s">
+      <c r="U3" s="359"/>
+      <c r="V3" s="360"/>
+      <c r="W3" s="351" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="358" t="s">
+      <c r="X3" s="351" t="s">
         <v>162</v>
       </c>
       <c r="AG3" s="124"/>
       <c r="AH3" s="124"/>
     </row>
-    <row r="4" spans="1:34" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="41" t="s">
         <v>50</v>
@@ -13379,17 +13392,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="349"/>
-      <c r="G4" s="355"/>
-      <c r="H4" s="355"/>
-      <c r="I4" s="349"/>
-      <c r="J4" s="349"/>
-      <c r="K4" s="349"/>
-      <c r="L4" s="349"/>
-      <c r="M4" s="349"/>
-      <c r="N4" s="361"/>
-      <c r="O4" s="361"/>
-      <c r="P4" s="360"/>
+      <c r="F4" s="347"/>
+      <c r="G4" s="348"/>
+      <c r="H4" s="348"/>
+      <c r="I4" s="347"/>
+      <c r="J4" s="347"/>
+      <c r="K4" s="347"/>
+      <c r="L4" s="347"/>
+      <c r="M4" s="347"/>
+      <c r="N4" s="354"/>
+      <c r="O4" s="354"/>
+      <c r="P4" s="353"/>
       <c r="Q4" s="194" t="s">
         <v>140</v>
       </c>
@@ -13408,10 +13421,10 @@
       <c r="V4" s="235" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="359"/>
-      <c r="X4" s="359"/>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="W4" s="352"/>
+      <c r="X4" s="352"/>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
         <v>46204</v>
       </c>
@@ -13478,7 +13491,7 @@
         <v>5175.6000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="201"/>
       <c r="B6" s="294">
         <v>36</v>
@@ -13545,7 +13558,7 @@
         <v>5175.6000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="201"/>
       <c r="B7" s="294">
         <v>33</v>
@@ -13612,7 +13625,7 @@
         <v>1135.29</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="201"/>
       <c r="B8" s="294">
         <v>29</v>
@@ -13677,7 +13690,7 @@
         <v>1018.85</v>
       </c>
     </row>
-    <row r="9" spans="1:34" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="201"/>
       <c r="B9" s="294">
         <v>0</v>
@@ -13742,7 +13755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:34" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="201"/>
       <c r="B10" s="294">
         <v>4</v>
@@ -13807,7 +13820,7 @@
         <v>101.6</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="20"/>
       <c r="B11" s="119">
         <f>SUM(B5:B10)</f>
@@ -13879,7 +13892,7 @@
       </c>
       <c r="AA11" s="172"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="60">
         <f>A5+1</f>
         <v>46205</v>
@@ -13950,7 +13963,7 @@
       </c>
       <c r="Z12" s="124"/>
     </row>
-    <row r="13" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="201"/>
       <c r="B13" s="294">
         <v>36</v>
@@ -14016,7 +14029,7 @@
       </c>
       <c r="Z13" s="124"/>
     </row>
-    <row r="14" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="201"/>
       <c r="B14" s="294">
         <v>33</v>
@@ -14084,7 +14097,7 @@
       </c>
       <c r="Z14" s="124"/>
     </row>
-    <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="201"/>
       <c r="B15" s="294">
         <v>29</v>
@@ -14149,7 +14162,7 @@
         <v>1018.85</v>
       </c>
     </row>
-    <row r="16" spans="1:34" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="201"/>
       <c r="B16" s="294">
         <v>0</v>
@@ -15877,8 +15890,8 @@
       <c r="U41" s="216"/>
       <c r="V41" s="228"/>
       <c r="W41" s="185">
-        <f>J41-(T41*($M$2-$K$1)+(U41*($M$2-$M$1)))-AH2</f>
-        <v>5019.420000000001</v>
+        <f>J41-(T41*($M$2-$K$1)+(U41*($M$2-$M$1)))-AJ2</f>
+        <v>5009.7500000000009</v>
       </c>
       <c r="X41" s="182">
         <f>H41*$M$2</f>
@@ -16228,7 +16241,7 @@
       </c>
       <c r="O46" s="21">
         <f>(W46/N46)*100</f>
-        <v>95.441871418478684</v>
+        <v>95.365962791427918</v>
       </c>
       <c r="P46" s="192"/>
       <c r="Q46" s="181"/>
@@ -16239,7 +16252,7 @@
       <c r="V46" s="181"/>
       <c r="W46" s="193">
         <f>SUM(W40:W45)</f>
-        <v>12158.34</v>
+        <v>12148.670000000002</v>
       </c>
       <c r="X46" s="193">
         <f>SUM(X40:X45)</f>
@@ -17274,7 +17287,7 @@
       </c>
     </row>
     <row r="62" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="346" t="s">
+      <c r="A62" s="368" t="s">
         <v>185</v>
       </c>
       <c r="B62" s="294">
@@ -17346,7 +17359,7 @@
       <c r="AB62" s="124"/>
     </row>
     <row r="63" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A63" s="346"/>
+      <c r="A63" s="368"/>
       <c r="B63" s="294">
         <v>36</v>
       </c>
@@ -17412,7 +17425,7 @@
       <c r="Y63" s="236"/>
     </row>
     <row r="64" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A64" s="346"/>
+      <c r="A64" s="368"/>
       <c r="B64" s="294">
         <v>32</v>
       </c>
@@ -17479,7 +17492,7 @@
       </c>
     </row>
     <row r="65" spans="1:27" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="346"/>
+      <c r="A65" s="368"/>
       <c r="B65" s="294">
         <v>0</v>
       </c>
@@ -17544,7 +17557,7 @@
       </c>
     </row>
     <row r="66" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="346"/>
+      <c r="A66" s="368"/>
       <c r="B66" s="294">
         <v>4</v>
       </c>
@@ -27988,38 +28001,38 @@
     <row r="222" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="223" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223"/>
-      <c r="B223" s="352" t="s">
+      <c r="B223" s="363" t="s">
         <v>56</v>
       </c>
-      <c r="C223" s="353"/>
-      <c r="D223" s="353"/>
-      <c r="E223" s="353"/>
-      <c r="F223" s="353"/>
-      <c r="G223" s="354"/>
+      <c r="C223" s="364"/>
+      <c r="D223" s="364"/>
+      <c r="E223" s="364"/>
+      <c r="F223" s="364"/>
+      <c r="G223" s="365"/>
       <c r="H223" s="289"/>
-      <c r="I223" s="352" t="s">
+      <c r="I223" s="363" t="s">
         <v>57</v>
       </c>
-      <c r="J223" s="353"/>
-      <c r="K223" s="353"/>
-      <c r="L223" s="353"/>
-      <c r="M223" s="353"/>
-      <c r="N223" s="354"/>
-      <c r="P223" s="368" t="s">
+      <c r="J223" s="364"/>
+      <c r="K223" s="364"/>
+      <c r="L223" s="364"/>
+      <c r="M223" s="364"/>
+      <c r="N223" s="365"/>
+      <c r="P223" s="361" t="s">
         <v>139</v>
       </c>
-      <c r="Q223" s="368"/>
-      <c r="R223" s="368"/>
-      <c r="S223" s="369"/>
-      <c r="T223" s="365" t="s">
+      <c r="Q223" s="361"/>
+      <c r="R223" s="361"/>
+      <c r="S223" s="362"/>
+      <c r="T223" s="358" t="s">
         <v>142</v>
       </c>
-      <c r="U223" s="366"/>
-      <c r="V223" s="367"/>
-      <c r="W223" s="356" t="s">
+      <c r="U223" s="359"/>
+      <c r="V223" s="360"/>
+      <c r="W223" s="349" t="s">
         <v>143</v>
       </c>
-      <c r="X223" s="356" t="s">
+      <c r="X223" s="349" t="s">
         <v>162</v>
       </c>
     </row>
@@ -28085,8 +28098,8 @@
       <c r="V224" s="226" t="s">
         <v>146</v>
       </c>
-      <c r="W224" s="357"/>
-      <c r="X224" s="357"/>
+      <c r="W224" s="350"/>
+      <c r="X224" s="350"/>
     </row>
     <row r="225" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
@@ -28172,7 +28185,7 @@
       </c>
       <c r="W225" s="230">
         <f>W11+W18+W25+W32+W39+W46+W53+W60+W67+W74+W81+W88+W95+W102+W109+W116+W123+W130+W137+W144+W151+W158+W165+W172+W179+W186+W193+W200+W207+W214</f>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="X225" s="230">
         <f>X11+X18+X25+X32+X39+X46+X53+X60+X67+X74+X81+X88+X95+X102+X109+X116+X123+X130+X137+X144+X151+X158+X165+X172+X179+X186+X193+X200+X207+X214</f>
@@ -28596,10 +28609,10 @@
     </row>
     <row r="235" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A235" s="24"/>
-      <c r="B235" s="350" t="s">
+      <c r="B235" s="366" t="s">
         <v>55</v>
       </c>
-      <c r="C235" s="351"/>
+      <c r="C235" s="367"/>
       <c r="D235" s="25" t="s">
         <v>65</v>
       </c>
@@ -28775,6 +28788,17 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="27">
+    <mergeCell ref="A62:A66"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="B235:C235"/>
+    <mergeCell ref="B223:G223"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="H3:H4"/>
@@ -28791,17 +28815,6 @@
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="I223:N223"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="B235:C235"/>
-    <mergeCell ref="B223:G223"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="A62:A66"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="D187:E192 D180:E185 D173:E178 D194:E199">
     <cfRule type="expression" dxfId="46" priority="190">
@@ -29060,126 +29073,126 @@
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="C1" s="8"/>
-      <c r="D1" s="370">
+      <c r="D1" s="371">
         <v>46204</v>
       </c>
-      <c r="E1" s="370"/>
-      <c r="F1" s="370">
+      <c r="E1" s="371"/>
+      <c r="F1" s="371">
         <v>46205</v>
       </c>
-      <c r="G1" s="370"/>
-      <c r="H1" s="370">
+      <c r="G1" s="371"/>
+      <c r="H1" s="371">
         <v>46206</v>
       </c>
-      <c r="I1" s="370"/>
-      <c r="J1" s="370">
+      <c r="I1" s="371"/>
+      <c r="J1" s="371">
         <v>46207</v>
       </c>
-      <c r="K1" s="370"/>
-      <c r="L1" s="370">
+      <c r="K1" s="371"/>
+      <c r="L1" s="371">
         <v>46208</v>
       </c>
-      <c r="M1" s="370"/>
-      <c r="N1" s="370">
+      <c r="M1" s="371"/>
+      <c r="N1" s="371">
         <v>46209</v>
       </c>
-      <c r="O1" s="370"/>
-      <c r="P1" s="370">
+      <c r="O1" s="371"/>
+      <c r="P1" s="371">
         <v>46210</v>
       </c>
-      <c r="Q1" s="370"/>
-      <c r="R1" s="370">
+      <c r="Q1" s="371"/>
+      <c r="R1" s="371">
         <v>46211</v>
       </c>
-      <c r="S1" s="370"/>
-      <c r="T1" s="370">
+      <c r="S1" s="371"/>
+      <c r="T1" s="371">
         <v>46212</v>
       </c>
-      <c r="U1" s="370"/>
-      <c r="V1" s="370">
+      <c r="U1" s="371"/>
+      <c r="V1" s="371">
         <v>46213</v>
       </c>
-      <c r="W1" s="370"/>
-      <c r="X1" s="370">
+      <c r="W1" s="371"/>
+      <c r="X1" s="371">
         <v>46214</v>
       </c>
-      <c r="Y1" s="370"/>
-      <c r="Z1" s="370">
+      <c r="Y1" s="371"/>
+      <c r="Z1" s="371">
         <v>46215</v>
       </c>
-      <c r="AA1" s="370"/>
-      <c r="AB1" s="370">
+      <c r="AA1" s="371"/>
+      <c r="AB1" s="371">
         <v>46216</v>
       </c>
-      <c r="AC1" s="370"/>
-      <c r="AD1" s="370">
+      <c r="AC1" s="371"/>
+      <c r="AD1" s="371">
         <v>46217</v>
       </c>
-      <c r="AE1" s="370"/>
-      <c r="AF1" s="370">
+      <c r="AE1" s="371"/>
+      <c r="AF1" s="371">
         <v>46218</v>
       </c>
-      <c r="AG1" s="370"/>
-      <c r="AH1" s="370">
+      <c r="AG1" s="371"/>
+      <c r="AH1" s="371">
         <v>46219</v>
       </c>
-      <c r="AI1" s="370"/>
-      <c r="AJ1" s="370">
+      <c r="AI1" s="371"/>
+      <c r="AJ1" s="371">
         <v>46220</v>
       </c>
-      <c r="AK1" s="370"/>
-      <c r="AL1" s="370">
+      <c r="AK1" s="371"/>
+      <c r="AL1" s="371">
         <v>46221</v>
       </c>
-      <c r="AM1" s="370"/>
-      <c r="AN1" s="370">
+      <c r="AM1" s="371"/>
+      <c r="AN1" s="371">
         <v>46222</v>
       </c>
-      <c r="AO1" s="370"/>
-      <c r="AP1" s="370">
+      <c r="AO1" s="371"/>
+      <c r="AP1" s="371">
         <v>46223</v>
       </c>
-      <c r="AQ1" s="370"/>
-      <c r="AR1" s="370">
+      <c r="AQ1" s="371"/>
+      <c r="AR1" s="371">
         <v>46224</v>
       </c>
-      <c r="AS1" s="370"/>
-      <c r="AT1" s="370">
+      <c r="AS1" s="371"/>
+      <c r="AT1" s="371">
         <v>46225</v>
       </c>
-      <c r="AU1" s="370"/>
-      <c r="AV1" s="370">
+      <c r="AU1" s="371"/>
+      <c r="AV1" s="371">
         <v>46226</v>
       </c>
-      <c r="AW1" s="370"/>
-      <c r="AX1" s="370">
+      <c r="AW1" s="371"/>
+      <c r="AX1" s="371">
         <v>46227</v>
       </c>
-      <c r="AY1" s="370"/>
-      <c r="AZ1" s="370">
+      <c r="AY1" s="371"/>
+      <c r="AZ1" s="371">
         <v>46228</v>
       </c>
-      <c r="BA1" s="370"/>
-      <c r="BB1" s="370">
+      <c r="BA1" s="371"/>
+      <c r="BB1" s="371">
         <v>46229</v>
       </c>
-      <c r="BC1" s="370"/>
-      <c r="BD1" s="370">
+      <c r="BC1" s="371"/>
+      <c r="BD1" s="371">
         <v>46230</v>
       </c>
-      <c r="BE1" s="370"/>
-      <c r="BF1" s="370">
+      <c r="BE1" s="371"/>
+      <c r="BF1" s="371">
         <v>46231</v>
       </c>
-      <c r="BG1" s="370"/>
-      <c r="BH1" s="370">
+      <c r="BG1" s="371"/>
+      <c r="BH1" s="371">
         <v>46232</v>
       </c>
-      <c r="BI1" s="370"/>
-      <c r="BJ1" s="370">
+      <c r="BI1" s="371"/>
+      <c r="BJ1" s="371">
         <v>46233</v>
       </c>
-      <c r="BK1" s="370"/>
+      <c r="BK1" s="371"/>
     </row>
     <row r="2" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="8"/>
@@ -33609,10 +33622,10 @@
       </c>
     </row>
     <row r="37" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A37" s="371" t="s">
+      <c r="A37" s="372" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="371"/>
+      <c r="B37" s="372"/>
       <c r="C37" s="8"/>
       <c r="D37" s="149">
         <f t="shared" ref="D37:AI37" si="14">SUM(D31:D36)</f>
@@ -36069,6 +36082,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="X1:Y1"/>
     <mergeCell ref="BH1:BI1"/>
     <mergeCell ref="BJ1:BK1"/>
     <mergeCell ref="AB1:AC1"/>
@@ -36085,21 +36113,6 @@
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AZ1:BA1"/>
     <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="X1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -39798,19 +39811,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="44.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="372" t="s">
+      <c r="A2" s="373" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="373"/>
-      <c r="C2" s="373"/>
-      <c r="D2" s="373"/>
-      <c r="E2" s="373"/>
-      <c r="F2" s="373"/>
-      <c r="G2" s="373"/>
-      <c r="H2" s="373"/>
-      <c r="I2" s="373"/>
-      <c r="J2" s="373"/>
-      <c r="K2" s="373"/>
+      <c r="B2" s="374"/>
+      <c r="C2" s="374"/>
+      <c r="D2" s="374"/>
+      <c r="E2" s="374"/>
+      <c r="F2" s="374"/>
+      <c r="G2" s="374"/>
+      <c r="H2" s="374"/>
+      <c r="I2" s="374"/>
+      <c r="J2" s="374"/>
+      <c r="K2" s="374"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="158" t="s">
@@ -40071,15 +40084,15 @@
       </c>
       <c r="D9" s="311">
         <f>'KM-Servicio'!W46</f>
-        <v>12158.34</v>
+        <v>12148.670000000002</v>
       </c>
       <c r="E9" s="311">
         <f t="shared" si="1"/>
-        <v>60804.72</v>
+        <v>60795.05</v>
       </c>
       <c r="F9" s="312">
         <f>'KM-Servicio'!O46</f>
-        <v>95.441871418478684</v>
+        <v>95.365962791427918</v>
       </c>
       <c r="G9" s="313">
         <f>SUM('KM-Servicio'!B46:C46)</f>
@@ -40117,7 +40130,7 @@
       </c>
       <c r="E10" s="311">
         <f t="shared" si="1"/>
-        <v>72930.81</v>
+        <v>72921.14</v>
       </c>
       <c r="F10" s="312">
         <f>'KM-Servicio'!O53</f>
@@ -40159,7 +40172,7 @@
       </c>
       <c r="E11" s="311">
         <f t="shared" si="1"/>
-        <v>85089.22</v>
+        <v>85079.55</v>
       </c>
       <c r="F11" s="312">
         <f>'KM-Servicio'!O60</f>
@@ -40201,7 +40214,7 @@
       </c>
       <c r="E12" s="12">
         <f t="shared" si="1"/>
-        <v>96434.51</v>
+        <v>96424.84</v>
       </c>
       <c r="F12" s="166">
         <f>'KM-Servicio'!O67</f>
@@ -40243,7 +40256,7 @@
       </c>
       <c r="E13" s="12">
         <f t="shared" si="1"/>
-        <v>107811.55</v>
+        <v>107801.88</v>
       </c>
       <c r="F13" s="166">
         <f>'KM-Servicio'!O74</f>
@@ -40285,7 +40298,7 @@
       </c>
       <c r="E14" s="12">
         <f t="shared" si="1"/>
-        <v>114281.05</v>
+        <v>114271.38</v>
       </c>
       <c r="F14" s="166">
         <f>'KM-Servicio'!O81</f>
@@ -40327,7 +40340,7 @@
       </c>
       <c r="E15" s="12">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F15" s="166">
         <f>'KM-Servicio'!O88</f>
@@ -40369,7 +40382,7 @@
       </c>
       <c r="E16" s="311">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F16" s="312">
         <f>'KM-Servicio'!O95</f>
@@ -40411,7 +40424,7 @@
       </c>
       <c r="E17" s="311">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F17" s="312" t="e">
         <f>'KM-Servicio'!O102</f>
@@ -40453,7 +40466,7 @@
       </c>
       <c r="E18" s="12">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F18" s="166" t="e">
         <f>'KM-Servicio'!O109</f>
@@ -40495,7 +40508,7 @@
       </c>
       <c r="E19" s="12">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F19" s="166" t="e">
         <f>'KM-Servicio'!O116</f>
@@ -40536,7 +40549,7 @@
       </c>
       <c r="E20" s="12">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F20" s="166" t="e">
         <f>'KM-Servicio'!O123</f>
@@ -40578,7 +40591,7 @@
       </c>
       <c r="E21" s="12">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F21" s="166" t="e">
         <f>'KM-Servicio'!O130</f>
@@ -40620,7 +40633,7 @@
       </c>
       <c r="E22" s="12">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F22" s="171" t="e">
         <f>'KM-Servicio'!O137</f>
@@ -40662,7 +40675,7 @@
       </c>
       <c r="E23" s="311">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F23" s="312" t="e">
         <f>'KM-Servicio'!O144</f>
@@ -40704,7 +40717,7 @@
       </c>
       <c r="E24" s="311">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F24" s="312" t="e">
         <f>'KM-Servicio'!O151</f>
@@ -40746,7 +40759,7 @@
       </c>
       <c r="E25" s="12">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F25" s="166" t="e">
         <f>'KM-Servicio'!O158</f>
@@ -40788,7 +40801,7 @@
       </c>
       <c r="E26" s="12">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F26" s="166" t="e">
         <f>'KM-Servicio'!O165</f>
@@ -40830,7 +40843,7 @@
       </c>
       <c r="E27" s="12">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F27" s="166" t="e">
         <f>'KM-Servicio'!O172</f>
@@ -40872,7 +40885,7 @@
       </c>
       <c r="E28" s="311">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F28" s="312" t="e">
         <f>'KM-Servicio'!O179</f>
@@ -40914,7 +40927,7 @@
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F29" s="166" t="e">
         <f>'KM-Servicio'!O186</f>
@@ -40956,7 +40969,7 @@
       </c>
       <c r="E30" s="311">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F30" s="312" t="e">
         <f>'KM-Servicio'!O193</f>
@@ -40998,7 +41011,7 @@
       </c>
       <c r="E31" s="311">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F31" s="312" t="e">
         <f>'KM-Servicio'!O200</f>
@@ -41040,7 +41053,7 @@
       </c>
       <c r="E32" s="311">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F32" s="312" t="e">
         <f>'KM-Servicio'!O207</f>
@@ -41082,11 +41095,11 @@
       </c>
       <c r="E33" s="311">
         <f t="shared" si="1"/>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O46</f>
-        <v>95.441871418478684</v>
+        <v>95.365962791427918</v>
       </c>
       <c r="G33" s="167">
         <f>'KM-Servicio'!B214+'KM-Servicio'!C214</f>
@@ -41154,11 +41167,11 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>119197.87000000001</v>
+        <v>119188.20000000001</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>2969234.4800000018</v>
+        <v>2968992.7300000009</v>
       </c>
       <c r="F36" s="170" t="e">
         <f>AVERAGE(F4:F34)</f>
@@ -41409,8 +41422,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="374"/>
-      <c r="H16" s="374"/>
+      <c r="G16" s="384"/>
+      <c r="H16" s="384"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -41425,8 +41438,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="374"/>
-      <c r="H17" s="374"/>
+      <c r="G17" s="384"/>
+      <c r="H17" s="384"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -41441,8 +41454,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="374"/>
-      <c r="H18" s="374"/>
+      <c r="G18" s="384"/>
+      <c r="H18" s="384"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -41456,8 +41469,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="374"/>
-      <c r="H19" s="374"/>
+      <c r="G19" s="384"/>
+      <c r="H19" s="384"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -41471,8 +41484,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="374"/>
-      <c r="H20" s="374"/>
+      <c r="G20" s="384"/>
+      <c r="H20" s="384"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -41486,8 +41499,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="374"/>
-      <c r="H21" s="374"/>
+      <c r="G21" s="384"/>
+      <c r="H21" s="384"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -41777,17 +41790,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
